--- a/Data/Rules/Glacier Peak Rules Matrix.xlsx
+++ b/Data/Rules/Glacier Peak Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>13934</t>
@@ -498,10 +501,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -622,504 +625,519 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>2</v>
+      </c>
+      <c r="Y2">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>2</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
+      <c r="AH2">
+        <v>3</v>
+      </c>
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>2</v>
+      </c>
+      <c r="Y3">
+        <v>3</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>2</v>
+      </c>
+      <c r="AH4">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>3</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>2</v>
+      </c>
+      <c r="AH5">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B6" t="s">
         <v>50</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>2</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>2</v>
-      </c>
-      <c r="V2">
-        <v>3</v>
-      </c>
-      <c r="W2" t="b">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>2</v>
-      </c>
-      <c r="Y2">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
-        <v>2</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>2</v>
-      </c>
-      <c r="AH2">
-        <v>3</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>1</v>
-      </c>
-      <c r="AK2">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40">
-      <c r="A3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>2</v>
-      </c>
-      <c r="V3">
-        <v>3</v>
-      </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>2</v>
-      </c>
-      <c r="Y3">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>2</v>
-      </c>
-      <c r="AH3">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>1</v>
-      </c>
-      <c r="AK3">
-        <v>2</v>
-      </c>
-      <c r="AL3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>2</v>
-      </c>
-      <c r="V4">
-        <v>3</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>2</v>
-      </c>
-      <c r="Y4">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>2</v>
-      </c>
-      <c r="AH4">
-        <v>3</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>1</v>
-      </c>
-      <c r="AK4">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5">
-        <v>3</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>2</v>
-      </c>
-      <c r="Y5">
-        <v>3</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-      <c r="AE5">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>2</v>
-      </c>
-      <c r="AH5">
-        <v>3</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>1</v>
-      </c>
-      <c r="AK5">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:40">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1231,6 +1249,9 @@
       </c>
       <c r="AN6">
         <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
